--- a/data/trans_orig/P29-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P29-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2007</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118612</t>
+          <t>118815</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160362</t>
+          <t>158453</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151639</t>
+          <t>152505</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>192606</t>
+          <t>192230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>283755</t>
+          <t>282384</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>338426</t>
+          <t>337130</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60284</t>
+          <t>61148</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92098</t>
+          <t>92650</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92931</t>
+          <t>93211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127483</t>
+          <t>128881</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161250</t>
+          <t>160685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208524</t>
+          <t>209833</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>259335</t>
+          <t>257532</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>302472</t>
+          <t>300753</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>166735</t>
+          <t>167329</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>209957</t>
+          <t>205063</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>439640</t>
+          <t>437139</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>498938</t>
+          <t>497498</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,74%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96675</t>
+          <t>97609</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139504</t>
+          <t>139493</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>225723</t>
+          <t>226336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>275200</t>
+          <t>275400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>336103</t>
+          <t>338245</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>403699</t>
+          <t>407626</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97890</t>
+          <t>96308</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>138066</t>
+          <t>138338</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>134393</t>
+          <t>134237</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>179561</t>
+          <t>177512</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>246502</t>
+          <t>245549</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>305973</t>
+          <t>302169</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>471305</t>
+          <t>474299</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>525647</t>
+          <t>528228</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>192532</t>
+          <t>194345</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>241616</t>
+          <t>244258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>681678</t>
+          <t>685092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>758154</t>
+          <t>755518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,51%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107958</t>
+          <t>108160</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>150637</t>
+          <t>150807</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>298031</t>
+          <t>297664</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>350436</t>
+          <t>351643</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>415006</t>
+          <t>414898</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>487413</t>
+          <t>484768</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92705</t>
+          <t>90576</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132129</t>
+          <t>128418</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>123336</t>
+          <t>122710</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164254</t>
+          <t>164770</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>226295</t>
+          <t>220431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>282449</t>
+          <t>279922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>374906</t>
+          <t>377685</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>422839</t>
+          <t>427695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>199503</t>
+          <t>196382</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>249154</t>
+          <t>248900</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>588658</t>
+          <t>591068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>663279</t>
+          <t>661943</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107239</t>
+          <t>107595</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>148020</t>
+          <t>147398</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>236924</t>
+          <t>238088</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>283077</t>
+          <t>283018</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>355890</t>
+          <t>355620</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>415141</t>
+          <t>419699</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63683</t>
+          <t>62830</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96918</t>
+          <t>98994</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90996</t>
+          <t>91506</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128415</t>
+          <t>128323</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>166490</t>
+          <t>166848</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>217117</t>
+          <t>214826</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>290163</t>
+          <t>289026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>335969</t>
+          <t>335495</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>127716</t>
+          <t>124055</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>167818</t>
+          <t>165279</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>425830</t>
+          <t>423839</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>490603</t>
+          <t>491628</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113346</t>
+          <t>112983</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>149442</t>
+          <t>149149</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223280</t>
+          <t>226088</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261897</t>
+          <t>263066</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>345909</t>
+          <t>344771</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>403232</t>
+          <t>401385</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,76%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61223</t>
+          <t>61159</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>92965</t>
+          <t>91615</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70807</t>
+          <t>68919</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>101456</t>
+          <t>101886</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137501</t>
+          <t>139477</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>184159</t>
+          <t>184774</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>160238</t>
+          <t>161479</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>199093</t>
+          <t>202234</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59939</t>
+          <t>60177</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91537</t>
+          <t>91146</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>229281</t>
+          <t>230652</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>282285</t>
+          <t>282956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>97420</t>
+          <t>97726</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>129288</t>
+          <t>130968</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>239565</t>
+          <t>239853</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>271139</t>
+          <t>270144</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>344870</t>
+          <t>345065</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>393433</t>
+          <t>394879</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38663</t>
+          <t>37862</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>63277</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44927</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>70936</t>
+          <t>70696</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>90529</t>
+          <t>90720</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>127335</t>
+          <t>126300</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>112577</t>
+          <t>111824</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>145848</t>
+          <t>146843</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21116</t>
+          <t>20287</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>41452</t>
+          <t>40696</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>139174</t>
+          <t>136978</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>181651</t>
+          <t>180712</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>86808</t>
+          <t>85840</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>115296</t>
+          <t>115020</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>267292</t>
+          <t>265688</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>293818</t>
+          <t>294303</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>358347</t>
+          <t>359092</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>402571</t>
+          <t>402726</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,06%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27412</t>
+          <t>26271</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46657</t>
+          <t>46828</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25299</t>
+          <t>25372</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>48497</t>
+          <t>48817</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>57287</t>
+          <t>56813</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>87597</t>
+          <t>88186</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>60246</t>
+          <t>60440</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>87335</t>
+          <t>87926</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27237</t>
+          <t>27874</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>73681</t>
+          <t>73018</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>110611</t>
+          <t>108810</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>804658</t>
+          <t>802564</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>906429</t>
+          <t>900023</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1728429</t>
+          <t>1719761</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1839822</t>
+          <t>1847016</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2556065</t>
+          <t>2563608</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2716679</t>
+          <t>2717815</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>500418</t>
+          <t>503282</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>586846</t>
+          <t>587875</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>653414</t>
+          <t>649158</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>748064</t>
+          <t>746706</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1174469</t>
+          <t>1177769</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1302182</t>
+          <t>1307266</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1821344</t>
+          <t>1829096</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1937089</t>
+          <t>1937077</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>844598</t>
+          <t>842806</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>949631</t>
+          <t>949667</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2705088</t>
+          <t>2701121</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2865563</t>
+          <t>2862436</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,01%</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2012</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96062</t>
+          <t>95055</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>133911</t>
+          <t>132518</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>163603</t>
+          <t>163170</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>203734</t>
+          <t>203884</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>270555</t>
+          <t>267580</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>325838</t>
+          <t>326181</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45059</t>
+          <t>45171</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74358</t>
+          <t>74641</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50268</t>
+          <t>47994</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79508</t>
+          <t>77435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102025</t>
+          <t>102215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141597</t>
+          <t>142214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>262042</t>
+          <t>261978</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>302790</t>
+          <t>304375</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>164213</t>
+          <t>164633</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>203943</t>
+          <t>205091</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>436904</t>
+          <t>437706</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>493552</t>
+          <t>497684</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,28%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>129436</t>
+          <t>130993</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176997</t>
+          <t>175807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>274965</t>
+          <t>272151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324882</t>
+          <t>323133</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>418898</t>
+          <t>417764</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>487528</t>
+          <t>491362</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,9%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50366</t>
+          <t>50155</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83577</t>
+          <t>82554</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78623</t>
+          <t>78453</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>115355</t>
+          <t>116446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>139256</t>
+          <t>138890</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187239</t>
+          <t>184768</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>442318</t>
+          <t>443949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>492431</t>
+          <t>490099</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>187278</t>
+          <t>190793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>235987</t>
+          <t>237792</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>644810</t>
+          <t>642870</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>717019</t>
+          <t>717269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,33%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>143638</t>
+          <t>143155</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>189652</t>
+          <t>190611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>326192</t>
+          <t>327134</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>381316</t>
+          <t>378924</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>479565</t>
+          <t>486045</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>555529</t>
+          <t>556231</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69414</t>
+          <t>70014</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106149</t>
+          <t>105705</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92255</t>
+          <t>93834</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132987</t>
+          <t>132363</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173251</t>
+          <t>170544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>225249</t>
+          <t>225279</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>403002</t>
+          <t>401187</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>455705</t>
+          <t>453223</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>217920</t>
+          <t>221242</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>272540</t>
+          <t>273721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>636962</t>
+          <t>632871</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>713647</t>
+          <t>709708</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>117113</t>
+          <t>118587</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>162575</t>
+          <t>160926</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>303049</t>
+          <t>303402</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>355426</t>
+          <t>355491</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>436161</t>
+          <t>436989</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>505645</t>
+          <t>504936</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65114</t>
+          <t>63889</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99211</t>
+          <t>98503</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56038</t>
+          <t>55410</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87521</t>
+          <t>87997</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126597</t>
+          <t>127776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176839</t>
+          <t>176733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>369564</t>
+          <t>368324</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>420214</t>
+          <t>417960</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>190941</t>
+          <t>191922</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>241988</t>
+          <t>244676</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>575077</t>
+          <t>577502</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>645868</t>
+          <t>648335</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,68%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>107429</t>
+          <t>106148</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>148519</t>
+          <t>146912</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>257712</t>
+          <t>257983</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>301018</t>
+          <t>298060</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>372515</t>
+          <t>373658</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>436843</t>
+          <t>436327</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,74%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56852</t>
+          <t>55477</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88253</t>
+          <t>86862</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43898</t>
+          <t>43904</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72473</t>
+          <t>72384</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>108172</t>
+          <t>105999</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>151741</t>
+          <t>149136</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>210637</t>
+          <t>210674</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>253551</t>
+          <t>253333</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92758</t>
+          <t>93905</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131231</t>
+          <t>131936</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>313476</t>
+          <t>314879</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>377016</t>
+          <t>375456</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>90655</t>
+          <t>90904</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>128103</t>
+          <t>124712</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>235152</t>
+          <t>234448</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>268145</t>
+          <t>269769</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>333235</t>
+          <t>333222</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>386856</t>
+          <t>384591</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,02%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34956</t>
+          <t>34793</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60770</t>
+          <t>59899</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33106</t>
+          <t>32020</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56470</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73513</t>
+          <t>74918</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>112519</t>
+          <t>109808</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>136950</t>
+          <t>137454</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>172752</t>
+          <t>174534</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>43192</t>
+          <t>42979</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73902</t>
+          <t>73614</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>184981</t>
+          <t>189459</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>237808</t>
+          <t>239787</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>117249</t>
+          <t>117576</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>151237</t>
+          <t>150471</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>313160</t>
+          <t>311365</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>343463</t>
+          <t>342633</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>439525</t>
+          <t>437213</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>487015</t>
+          <t>486914</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,22%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42322</t>
+          <t>42090</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>24107</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>47782</t>
+          <t>47704</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48459</t>
+          <t>49335</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>81708</t>
+          <t>81372</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>70470</t>
+          <t>70965</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>103113</t>
+          <t>100837</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>16355</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>36406</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>91183</t>
+          <t>91091</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>130904</t>
+          <t>132725</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>891280</t>
+          <t>893521</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1000145</t>
+          <t>998833</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1965565</t>
+          <t>1966518</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2087090</t>
+          <t>2088174</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2881319</t>
+          <t>2884297</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3047949</t>
+          <t>3053309</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>398228</t>
+          <t>399242</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>475914</t>
+          <t>480178</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>435303</t>
+          <t>433110</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>517018</t>
+          <t>519327</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>853749</t>
+          <t>857725</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>973490</t>
+          <t>973628</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1987829</t>
+          <t>1985146</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2106482</t>
+          <t>2105949</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>996922</t>
+          <t>1001655</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1112730</t>
+          <t>1109914</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3017216</t>
+          <t>3015447</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3185352</t>
+          <t>3184731</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2016</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2016 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60047</t>
+          <t>60455</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93531</t>
+          <t>93324</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88442</t>
+          <t>87991</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121997</t>
+          <t>121183</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155498</t>
+          <t>157246</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>204070</t>
+          <t>203881</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70275</t>
+          <t>69819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103297</t>
+          <t>104572</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103367</t>
+          <t>101365</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139057</t>
+          <t>135840</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>180538</t>
+          <t>182393</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>229798</t>
+          <t>231489</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>235488</t>
+          <t>236491</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>275469</t>
+          <t>278787</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>153450</t>
+          <t>152807</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>192511</t>
+          <t>190397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>402248</t>
+          <t>401257</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>458563</t>
+          <t>459518</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,44%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50398</t>
+          <t>50683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80395</t>
+          <t>81725</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>94035</t>
+          <t>90908</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>130367</t>
+          <t>129523</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152588</t>
+          <t>152622</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>202175</t>
+          <t>200793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>136799</t>
+          <t>137970</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>180786</t>
+          <t>179365</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>202542</t>
+          <t>200758</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247217</t>
+          <t>247205</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>353391</t>
+          <t>351859</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>416652</t>
+          <t>418228</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>343907</t>
+          <t>343674</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>392633</t>
+          <t>390297</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>205377</t>
+          <t>204193</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>249865</t>
+          <t>249859</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>559814</t>
+          <t>559037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>627288</t>
+          <t>627349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,41%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56567</t>
+          <t>56384</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90585</t>
+          <t>88976</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>141676</t>
+          <t>139016</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184602</t>
+          <t>183426</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>206323</t>
+          <t>207107</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>262552</t>
+          <t>262435</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141581</t>
+          <t>141988</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187294</t>
+          <t>186060</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>223665</t>
+          <t>221696</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>270754</t>
+          <t>269117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>380860</t>
+          <t>380649</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>444938</t>
+          <t>443536</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>405589</t>
+          <t>408897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>457409</t>
+          <t>459546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>226795</t>
+          <t>225084</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>275889</t>
+          <t>274629</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>646513</t>
+          <t>645068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>717148</t>
+          <t>716764</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,91%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59546</t>
+          <t>58186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94200</t>
+          <t>92769</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133103</t>
+          <t>133453</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>177775</t>
+          <t>177665</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>202338</t>
+          <t>200889</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>260223</t>
+          <t>258012</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154822</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202963</t>
+          <t>203508</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>202738</t>
+          <t>200859</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>251607</t>
+          <t>252156</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374380</t>
+          <t>374676</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>443902</t>
+          <t>443867</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>363957</t>
+          <t>363506</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>416834</t>
+          <t>415533</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>241415</t>
+          <t>243191</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>291823</t>
+          <t>293196</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>618727</t>
+          <t>616950</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>692220</t>
+          <t>692715</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,58%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46812</t>
+          <t>47577</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78069</t>
+          <t>79214</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>138209</t>
+          <t>138352</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>183215</t>
+          <t>182613</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>195017</t>
+          <t>195442</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>248629</t>
+          <t>249226</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>110519</t>
+          <t>109794</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>148607</t>
+          <t>150317</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>178639</t>
+          <t>180278</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>223832</t>
+          <t>226947</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>301273</t>
+          <t>300987</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>363740</t>
+          <t>361413</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,2%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>264159</t>
+          <t>263064</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>307664</t>
+          <t>308223</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112276</t>
+          <t>111908</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>153779</t>
+          <t>152763</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>388657</t>
+          <t>387042</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>450121</t>
+          <t>453356</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36361</t>
+          <t>36955</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>62042</t>
+          <t>62769</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>162316</t>
+          <t>161495</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>201552</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>206208</t>
+          <t>205699</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>259922</t>
+          <t>257980</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92002</t>
+          <t>91751</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>127945</t>
+          <t>125083</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>109868</t>
+          <t>109890</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>148949</t>
+          <t>146856</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>210115</t>
+          <t>210789</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>262547</t>
+          <t>262920</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>158484</t>
+          <t>158606</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>195375</t>
+          <t>195784</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52787</t>
+          <t>53178</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>84675</t>
+          <t>83285</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>220337</t>
+          <t>219300</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>269306</t>
+          <t>269392</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24864</t>
+          <t>24870</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45769</t>
+          <t>45478</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>226024</t>
+          <t>224071</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>267531</t>
+          <t>268292</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>254005</t>
+          <t>253352</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>308289</t>
+          <t>308004</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,87%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>112788</t>
+          <t>112008</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>140774</t>
+          <t>141968</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>97185</t>
+          <t>96646</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>138386</t>
+          <t>138089</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>217202</t>
+          <t>218689</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>269755</t>
+          <t>268897</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,92%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>83232</t>
+          <t>82848</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>111561</t>
+          <t>112226</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24899</t>
+          <t>24133</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53007</t>
+          <t>53908</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>112538</t>
+          <t>113476</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>155704</t>
+          <t>155867</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>390976</t>
+          <t>388623</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>470578</t>
+          <t>472713</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1059732</t>
+          <t>1070871</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1180103</t>
+          <t>1181127</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1475752</t>
+          <t>1484026</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1616346</t>
+          <t>1623633</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>903587</t>
+          <t>901417</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1007929</t>
+          <t>1006557</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1202870</t>
+          <t>1207095</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1314510</t>
+          <t>1330245</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2130797</t>
+          <t>2134026</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2288064</t>
+          <t>2299979</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1953610</t>
+          <t>1946076</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2064740</t>
+          <t>2064067</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1091427</t>
+          <t>1100340</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1209526</t>
+          <t>1213283</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3085536</t>
+          <t>3070648</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3250429</t>
+          <t>3246187</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2023</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48375</t>
+          <t>50081</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101460</t>
+          <t>104072</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72737</t>
+          <t>72989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115941</t>
+          <t>116454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>133332</t>
+          <t>130581</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>203362</t>
+          <t>199894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -12495,12 +12495,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91223</t>
+          <t>87529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159872</t>
+          <t>154141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57473</t>
+          <t>56243</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96303</t>
+          <t>94098</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158491</t>
+          <t>156003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>231385</t>
+          <t>233063</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -12608,12 +12608,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>171008</t>
+          <t>173692</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>238844</t>
+          <t>244122</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12643,12 +12643,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>123160</t>
+          <t>123531</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170423</t>
+          <t>171727</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>316261</t>
+          <t>314995</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>398091</t>
+          <t>396745</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,63%</t>
         </is>
       </c>
     </row>
@@ -12838,12 +12838,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47037</t>
+          <t>45378</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83674</t>
+          <t>80381</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54526</t>
+          <t>51520</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109737</t>
+          <t>108896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114561</t>
+          <t>114407</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176102</t>
+          <t>178238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -12951,12 +12951,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67849</t>
+          <t>67930</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>108399</t>
+          <t>110439</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94427</t>
+          <t>93087</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>183683</t>
+          <t>181457</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>183837</t>
+          <t>181968</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>278685</t>
+          <t>274951</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>247934</t>
+          <t>248251</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>295571</t>
+          <t>298668</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13079,12 +13079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>225734</t>
+          <t>228270</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>363991</t>
+          <t>372249</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13114,12 +13114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13134,12 +13134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>496065</t>
+          <t>499950</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>636649</t>
+          <t>633839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64617</t>
+          <t>65557</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>96479</t>
+          <t>97290</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13309,12 +13309,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13329,12 +13329,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113552</t>
+          <t>113018</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145770</t>
+          <t>146583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>189050</t>
+          <t>189167</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236641</t>
+          <t>234729</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13379,12 +13379,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -13407,12 +13407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95627</t>
+          <t>96436</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134579</t>
+          <t>134316</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13422,12 +13422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13442,12 +13442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172978</t>
+          <t>173139</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>208434</t>
+          <t>209237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13457,12 +13457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13477,12 +13477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>277708</t>
+          <t>278344</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>333455</t>
+          <t>331447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -13520,12 +13520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>316901</t>
+          <t>318446</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361839</t>
+          <t>364152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13555,12 +13555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203189</t>
+          <t>201890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>241072</t>
+          <t>239770</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13570,12 +13570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13590,12 +13590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>532242</t>
+          <t>532055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>594138</t>
+          <t>593359</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40210</t>
+          <t>42394</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135229</t>
+          <t>133647</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>183167</t>
+          <t>184313</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>299032</t>
+          <t>301506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>192727</t>
+          <t>189522</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>387463</t>
+          <t>389012</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13835,12 +13835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63550</t>
+          <t>74912</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>219329</t>
+          <t>217422</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13878,12 +13878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191193</t>
+          <t>186985</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>246120</t>
+          <t>246379</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>222430</t>
+          <t>233020</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>455743</t>
+          <t>456634</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13948,12 +13948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -13976,12 +13976,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>536945</t>
+          <t>538883</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>772867</t>
+          <t>764126</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>225948</t>
+          <t>228880</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>299269</t>
+          <t>300180</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14026,12 +14026,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>777702</t>
+          <t>775716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1204271</t>
+          <t>1182698</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>74,12%</t>
         </is>
       </c>
     </row>
@@ -14206,12 +14206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69827</t>
+          <t>70571</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101889</t>
+          <t>101692</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -14221,12 +14221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>154691</t>
+          <t>153885</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>186091</t>
+          <t>185424</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>231660</t>
+          <t>231921</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>277515</t>
+          <t>276518</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14291,12 +14291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -14319,12 +14319,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>135691</t>
+          <t>133779</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>174990</t>
+          <t>171122</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>168264</t>
+          <t>169826</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>202656</t>
+          <t>201931</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14369,12 +14369,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>313958</t>
+          <t>312554</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>364184</t>
+          <t>363452</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>299438</t>
+          <t>301425</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>343489</t>
+          <t>344197</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>172673</t>
+          <t>172965</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>206251</t>
+          <t>204594</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>484625</t>
+          <t>484810</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>540820</t>
+          <t>539160</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14517,12 +14517,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,81%</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47865</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>71746</t>
+          <t>71352</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>67210</t>
+          <t>65445</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>253210</t>
+          <t>252587</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>108663</t>
+          <t>109965</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>289707</t>
+          <t>291409</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14747,12 +14747,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -14775,12 +14775,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>80225</t>
+          <t>80611</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106726</t>
+          <t>107309</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58762</t>
+          <t>52687</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>209699</t>
+          <t>208662</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14825,12 +14825,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>107267</t>
+          <t>114887</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>294947</t>
+          <t>294124</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14888,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>198349</t>
+          <t>198495</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>230052</t>
+          <t>228994</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14903,12 +14903,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14923,12 +14923,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>153400</t>
+          <t>153774</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>482235</t>
+          <t>492074</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14938,12 +14938,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>397456</t>
+          <t>396074</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>762170</t>
+          <t>750887</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14973,12 +14973,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>77,01%</t>
         </is>
       </c>
     </row>
@@ -15118,12 +15118,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>42888</t>
+          <t>42756</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>63795</t>
+          <t>63700</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15148,17 +15148,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>213181</t>
+          <t>213180</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>198790</t>
+          <t>198715</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>226854</t>
+          <t>227711</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15188,12 +15188,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>247233</t>
+          <t>249263</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>286435</t>
+          <t>286583</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>94691</t>
+          <t>94436</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>119705</t>
+          <t>121063</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15246,12 +15246,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>150310</t>
+          <t>148723</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>178416</t>
+          <t>178448</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>251703</t>
+          <t>252921</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>290352</t>
+          <t>291418</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>109514</t>
+          <t>108863</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>135044</t>
+          <t>134634</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15379,12 +15379,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>38288</t>
+          <t>38291</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>56644</t>
+          <t>56427</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15399,7 +15399,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>151753</t>
+          <t>149821</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>187459</t>
+          <t>185239</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>396396</t>
+          <t>383287</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>565439</t>
+          <t>558848</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15589,12 +15589,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>878297</t>
+          <t>890681</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1159343</t>
+          <t>1170070</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15644,12 +15644,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1385623</t>
+          <t>1351442</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1711187</t>
+          <t>1693041</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15659,12 +15659,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>635049</t>
+          <t>619525</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>914387</t>
+          <t>910305</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15702,12 +15702,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>923005</t>
+          <t>901031</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1216084</t>
+          <t>1212287</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15737,12 +15737,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1707113</t>
+          <t>1646294</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2091596</t>
+          <t>2089340</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -15800,12 +15800,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1996465</t>
+          <t>2003440</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2414665</t>
+          <t>2454165</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15815,12 +15815,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1295822</t>
+          <t>1293512</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1857073</t>
+          <t>1861306</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3344938</t>
+          <t>3354584</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4003178</t>
+          <t>4110669</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P29-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P29-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118815</t>
+          <t>117623</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>158453</t>
+          <t>159744</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>152505</t>
+          <t>151308</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>192230</t>
+          <t>192424</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>282384</t>
+          <t>278773</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>337130</t>
+          <t>336301</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61148</t>
+          <t>58935</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92650</t>
+          <t>90253</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93211</t>
+          <t>92624</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128881</t>
+          <t>128927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160685</t>
+          <t>161758</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>209833</t>
+          <t>210865</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>257532</t>
+          <t>259100</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>300753</t>
+          <t>302609</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>167329</t>
+          <t>165162</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>205063</t>
+          <t>208849</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>437139</t>
+          <t>435963</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>497498</t>
+          <t>497876</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97609</t>
+          <t>98530</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139493</t>
+          <t>140626</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>226336</t>
+          <t>225795</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>275400</t>
+          <t>277509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>338245</t>
+          <t>334876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>407626</t>
+          <t>401838</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96308</t>
+          <t>97711</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>138338</t>
+          <t>136548</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>134237</t>
+          <t>136489</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>177512</t>
+          <t>181274</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>245549</t>
+          <t>246244</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>302169</t>
+          <t>307817</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>474299</t>
+          <t>476471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>528228</t>
+          <t>525525</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>194345</t>
+          <t>195302</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>244258</t>
+          <t>242972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>685092</t>
+          <t>680258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>755518</t>
+          <t>754007</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>108160</t>
+          <t>104765</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>150807</t>
+          <t>148052</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>297664</t>
+          <t>297890</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>351643</t>
+          <t>349876</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>414898</t>
+          <t>411300</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>484768</t>
+          <t>483722</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90576</t>
+          <t>91017</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128418</t>
+          <t>129171</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122710</t>
+          <t>121457</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164770</t>
+          <t>163653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>220431</t>
+          <t>223456</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>279922</t>
+          <t>281348</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>377685</t>
+          <t>378367</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>427695</t>
+          <t>428825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196382</t>
+          <t>199321</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>248900</t>
+          <t>248132</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>591068</t>
+          <t>590004</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>661943</t>
+          <t>665118</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,07%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107595</t>
+          <t>106809</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147398</t>
+          <t>147645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>238088</t>
+          <t>238274</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>283018</t>
+          <t>282887</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>355620</t>
+          <t>354624</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>419699</t>
+          <t>418810</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62830</t>
+          <t>64793</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98994</t>
+          <t>97355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>91506</t>
+          <t>94217</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128323</t>
+          <t>130198</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>166848</t>
+          <t>165063</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>214826</t>
+          <t>215553</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>289026</t>
+          <t>291418</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>335495</t>
+          <t>335952</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>124055</t>
+          <t>126547</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>165279</t>
+          <t>165528</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>423839</t>
+          <t>430676</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>491628</t>
+          <t>493780</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112983</t>
+          <t>113972</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>149149</t>
+          <t>150034</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>226088</t>
+          <t>223363</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>263066</t>
+          <t>263107</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>344771</t>
+          <t>347500</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>401385</t>
+          <t>402839</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61159</t>
+          <t>60344</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>91615</t>
+          <t>91715</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68919</t>
+          <t>68649</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>101886</t>
+          <t>101358</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>139477</t>
+          <t>139971</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>184774</t>
+          <t>184157</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>161479</t>
+          <t>161775</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>202234</t>
+          <t>197893</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60177</t>
+          <t>61432</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91146</t>
+          <t>91842</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230652</t>
+          <t>230593</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>282956</t>
+          <t>282874</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>97726</t>
+          <t>96816</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>130968</t>
+          <t>130412</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>239853</t>
+          <t>239685</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>270144</t>
+          <t>270676</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>345065</t>
+          <t>343261</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>394879</t>
+          <t>390443</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,44%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37862</t>
+          <t>38101</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>63449</t>
+          <t>63937</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45732</t>
+          <t>46063</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>70696</t>
+          <t>71814</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>90720</t>
+          <t>89680</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>126300</t>
+          <t>126322</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>111824</t>
+          <t>113058</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>146843</t>
+          <t>147278</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>20514</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40696</t>
+          <t>40811</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>136978</t>
+          <t>138679</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>180712</t>
+          <t>181496</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>85840</t>
+          <t>86281</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>115020</t>
+          <t>113704</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>265688</t>
+          <t>266004</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>294303</t>
+          <t>294797</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>359092</t>
+          <t>357289</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>402726</t>
+          <t>402329</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>27220</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46828</t>
+          <t>46959</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>25202</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>48817</t>
+          <t>48605</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>56813</t>
+          <t>57295</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>88186</t>
+          <t>89797</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>60440</t>
+          <t>59344</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>87926</t>
+          <t>87311</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>9669</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27874</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>73018</t>
+          <t>72997</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>108810</t>
+          <t>109695</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>802564</t>
+          <t>796874</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>900023</t>
+          <t>900685</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1719761</t>
+          <t>1732032</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1847016</t>
+          <t>1841319</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2563608</t>
+          <t>2553101</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2717815</t>
+          <t>2721330</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>503282</t>
+          <t>497623</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>587875</t>
+          <t>581705</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>649158</t>
+          <t>652015</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>746706</t>
+          <t>744606</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1177769</t>
+          <t>1175969</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1307266</t>
+          <t>1307369</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1829096</t>
+          <t>1828370</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1937077</t>
+          <t>1940337</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>842806</t>
+          <t>843828</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>949667</t>
+          <t>948671</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2701121</t>
+          <t>2701679</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2862436</t>
+          <t>2867395</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95055</t>
+          <t>96151</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132518</t>
+          <t>133065</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>163170</t>
+          <t>162439</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>203884</t>
+          <t>204839</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>267580</t>
+          <t>268139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>326181</t>
+          <t>326370</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45171</t>
+          <t>44506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74641</t>
+          <t>73346</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47994</t>
+          <t>47808</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77435</t>
+          <t>77078</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102215</t>
+          <t>102015</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>142214</t>
+          <t>142169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>261978</t>
+          <t>260177</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>304375</t>
+          <t>301520</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>164633</t>
+          <t>163895</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>205091</t>
+          <t>205259</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>437706</t>
+          <t>436384</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>497684</t>
+          <t>497214</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,22%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130993</t>
+          <t>131790</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>175807</t>
+          <t>176767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>272151</t>
+          <t>274635</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>323133</t>
+          <t>323960</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>417764</t>
+          <t>418237</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>491362</t>
+          <t>488687</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50155</t>
+          <t>51360</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82554</t>
+          <t>81016</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78453</t>
+          <t>78829</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116446</t>
+          <t>116328</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>138890</t>
+          <t>138088</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>184768</t>
+          <t>188476</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>443949</t>
+          <t>441183</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>490099</t>
+          <t>492137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>190793</t>
+          <t>190286</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>237792</t>
+          <t>238769</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>642870</t>
+          <t>644481</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>717269</t>
+          <t>716173</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>143155</t>
+          <t>141856</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>190611</t>
+          <t>188335</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>327134</t>
+          <t>328216</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>378924</t>
+          <t>382767</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>486045</t>
+          <t>483802</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>556231</t>
+          <t>558864</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70014</t>
+          <t>71104</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105705</t>
+          <t>105650</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93834</t>
+          <t>93077</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132363</t>
+          <t>133208</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170544</t>
+          <t>174525</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>225279</t>
+          <t>222509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>401187</t>
+          <t>403217</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>453223</t>
+          <t>454156</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>221242</t>
+          <t>220138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273721</t>
+          <t>271207</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>632871</t>
+          <t>634209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>709708</t>
+          <t>709991</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,98%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118587</t>
+          <t>118630</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160926</t>
+          <t>164083</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>303402</t>
+          <t>301809</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>355491</t>
+          <t>354426</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>436989</t>
+          <t>435713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>504936</t>
+          <t>509353</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63889</t>
+          <t>63993</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98503</t>
+          <t>99774</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55410</t>
+          <t>54693</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87997</t>
+          <t>88038</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>127776</t>
+          <t>128522</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176733</t>
+          <t>177717</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>368324</t>
+          <t>370165</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>417960</t>
+          <t>420159</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191922</t>
+          <t>193232</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>244676</t>
+          <t>241751</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>577502</t>
+          <t>569966</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>648335</t>
+          <t>647698</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>106148</t>
+          <t>107906</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>146912</t>
+          <t>147263</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>257983</t>
+          <t>255597</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>298060</t>
+          <t>299425</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>373658</t>
+          <t>377784</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>436327</t>
+          <t>438191</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,95%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55477</t>
+          <t>56552</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>86862</t>
+          <t>88912</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43904</t>
+          <t>43375</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72384</t>
+          <t>72292</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>105999</t>
+          <t>107196</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>149136</t>
+          <t>149547</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>210674</t>
+          <t>210104</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>253333</t>
+          <t>254375</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93905</t>
+          <t>93231</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131936</t>
+          <t>133884</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>314879</t>
+          <t>312066</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>375456</t>
+          <t>371545</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>90904</t>
+          <t>91329</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>124712</t>
+          <t>126270</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>234448</t>
+          <t>234204</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>269769</t>
+          <t>269143</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>333222</t>
+          <t>330848</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>384591</t>
+          <t>385423</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34793</t>
+          <t>34659</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59899</t>
+          <t>61346</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32020</t>
+          <t>33159</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>56733</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74918</t>
+          <t>75491</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>109808</t>
+          <t>112538</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>137454</t>
+          <t>134912</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>174534</t>
+          <t>172823</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42979</t>
+          <t>43734</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73614</t>
+          <t>72303</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>189459</t>
+          <t>187893</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>239787</t>
+          <t>236560</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>117576</t>
+          <t>117750</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>150471</t>
+          <t>151414</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>311365</t>
+          <t>315783</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>342633</t>
+          <t>343878</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>437213</t>
+          <t>440008</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>486914</t>
+          <t>487644</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,33%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19808</t>
+          <t>20451</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42090</t>
+          <t>41297</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24107</t>
+          <t>24524</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>47704</t>
+          <t>47121</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49335</t>
+          <t>49849</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>81372</t>
+          <t>82167</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>70965</t>
+          <t>70292</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>100837</t>
+          <t>101096</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16355</t>
+          <t>15588</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>36406</t>
+          <t>36253</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>91091</t>
+          <t>91241</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>132725</t>
+          <t>132417</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>893521</t>
+          <t>892673</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>998833</t>
+          <t>998843</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1966518</t>
+          <t>1963381</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2088174</t>
+          <t>2080431</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2884297</t>
+          <t>2891285</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3053309</t>
+          <t>3068938</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>399242</t>
+          <t>398961</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>480178</t>
+          <t>477955</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>433110</t>
+          <t>434993</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>519327</t>
+          <t>516339</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>857725</t>
+          <t>856922</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>973628</t>
+          <t>972565</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1985146</t>
+          <t>1981186</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2105949</t>
+          <t>2098895</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1001655</t>
+          <t>996368</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1109914</t>
+          <t>1109880</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3015447</t>
+          <t>3001921</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3184731</t>
+          <t>3184643</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,6%</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60455</t>
+          <t>60833</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93324</t>
+          <t>92473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87991</t>
+          <t>88264</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121183</t>
+          <t>122492</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>157246</t>
+          <t>155891</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>203881</t>
+          <t>201564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69819</t>
+          <t>70111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104572</t>
+          <t>104251</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101365</t>
+          <t>101813</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135840</t>
+          <t>139983</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>182393</t>
+          <t>181142</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>231489</t>
+          <t>229741</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>236491</t>
+          <t>237413</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>278787</t>
+          <t>275306</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>152807</t>
+          <t>152384</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>190397</t>
+          <t>191365</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>401257</t>
+          <t>401367</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>459518</t>
+          <t>456620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,09%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50683</t>
+          <t>51073</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81725</t>
+          <t>81013</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90908</t>
+          <t>92467</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>129523</t>
+          <t>129297</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152622</t>
+          <t>154235</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>200793</t>
+          <t>202344</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>137970</t>
+          <t>136331</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>179365</t>
+          <t>181279</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>200758</t>
+          <t>199651</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247205</t>
+          <t>246598</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>351859</t>
+          <t>354132</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>418228</t>
+          <t>416738</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>343674</t>
+          <t>343290</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>390297</t>
+          <t>391159</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204193</t>
+          <t>204490</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>249859</t>
+          <t>250900</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>559037</t>
+          <t>557567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>627349</t>
+          <t>625032</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,21%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56384</t>
+          <t>57613</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88976</t>
+          <t>90189</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>139016</t>
+          <t>141790</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183426</t>
+          <t>184971</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>207107</t>
+          <t>203854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>262435</t>
+          <t>260773</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141988</t>
+          <t>141788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>186060</t>
+          <t>188490</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>221696</t>
+          <t>221068</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>269117</t>
+          <t>270723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>380649</t>
+          <t>379664</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>443536</t>
+          <t>448871</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>408897</t>
+          <t>406321</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>459546</t>
+          <t>457869</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>225084</t>
+          <t>228538</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274629</t>
+          <t>276218</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>645068</t>
+          <t>646291</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>716764</t>
+          <t>719035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58186</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92769</t>
+          <t>95912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133453</t>
+          <t>132575</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>177665</t>
+          <t>176352</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>200889</t>
+          <t>202587</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>258012</t>
+          <t>261742</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154620</t>
+          <t>156255</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203508</t>
+          <t>204368</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200859</t>
+          <t>201885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>252156</t>
+          <t>250858</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374676</t>
+          <t>369095</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>443867</t>
+          <t>441185</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>363506</t>
+          <t>367002</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>415533</t>
+          <t>418187</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>243191</t>
+          <t>241339</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>293196</t>
+          <t>291816</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>616950</t>
+          <t>622075</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>692715</t>
+          <t>698184</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47577</t>
+          <t>48576</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79214</t>
+          <t>77619</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>138352</t>
+          <t>137370</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>182613</t>
+          <t>181762</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>195442</t>
+          <t>195593</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>249226</t>
+          <t>250208</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>109794</t>
+          <t>109641</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>150317</t>
+          <t>149312</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>180278</t>
+          <t>182714</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>226947</t>
+          <t>225516</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>300987</t>
+          <t>301979</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>361413</t>
+          <t>365233</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,6%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>263064</t>
+          <t>263226</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>308223</t>
+          <t>308236</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>111908</t>
+          <t>110212</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152763</t>
+          <t>151705</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>387042</t>
+          <t>388637</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>453356</t>
+          <t>452085</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36955</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>62769</t>
+          <t>64185</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>161495</t>
+          <t>163589</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>201552</t>
+          <t>202812</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>205699</t>
+          <t>205263</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>257980</t>
+          <t>256917</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>91751</t>
+          <t>92403</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125083</t>
+          <t>125220</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>109890</t>
+          <t>109021</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>146856</t>
+          <t>144224</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>210789</t>
+          <t>211628</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>262920</t>
+          <t>260014</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>158606</t>
+          <t>159537</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>195784</t>
+          <t>195261</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53178</t>
+          <t>52779</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>83285</t>
+          <t>84242</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>219300</t>
+          <t>219673</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>269392</t>
+          <t>271065</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,07%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24870</t>
+          <t>24860</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45478</t>
+          <t>44466</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>224071</t>
+          <t>227040</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>268292</t>
+          <t>269754</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>253352</t>
+          <t>255570</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>308004</t>
+          <t>308307</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,91%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>112008</t>
+          <t>113734</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>141968</t>
+          <t>141392</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>96646</t>
+          <t>96683</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>138089</t>
+          <t>136056</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>218689</t>
+          <t>219230</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>268897</t>
+          <t>269429</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,0%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>82848</t>
+          <t>81538</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>112226</t>
+          <t>109891</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24133</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53908</t>
+          <t>51452</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>113476</t>
+          <t>114970</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>155867</t>
+          <t>157090</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>388623</t>
+          <t>390363</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>472713</t>
+          <t>473128</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1070871</t>
+          <t>1061831</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1181127</t>
+          <t>1178938</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1484026</t>
+          <t>1486244</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1623633</t>
+          <t>1624104</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>901417</t>
+          <t>900709</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1006557</t>
+          <t>1009819</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1207095</t>
+          <t>1206070</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1330245</t>
+          <t>1323384</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2134026</t>
+          <t>2135072</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2299979</t>
+          <t>2291141</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1946076</t>
+          <t>1946450</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2064067</t>
+          <t>2064329</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,7 +11932,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1100340</t>
+          <t>1094164</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1213283</t>
+          <t>1212388</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3070648</t>
+          <t>3074050</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3246187</t>
+          <t>3240334</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,76%</t>
         </is>
       </c>
     </row>
@@ -12377,32 +12377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>71770</t>
+          <t>89124</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50081</t>
+          <t>65972</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104072</t>
+          <t>118393</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>92925</t>
+          <t>118810</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72989</t>
+          <t>95101</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116454</t>
+          <t>145904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>164694</t>
+          <t>207933</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>130581</t>
+          <t>171881</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199894</t>
+          <t>246843</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -12490,32 +12490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>119559</t>
+          <t>114334</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87529</t>
+          <t>87104</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154141</t>
+          <t>143159</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12525,32 +12525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73820</t>
+          <t>84663</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56243</t>
+          <t>64005</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94098</t>
+          <t>105050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>193379</t>
+          <t>198997</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156003</t>
+          <t>165637</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>233063</t>
+          <t>241429</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -12603,32 +12603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>208658</t>
+          <t>204336</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>173692</t>
+          <t>172408</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>244122</t>
+          <t>233534</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12638,32 +12638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>146455</t>
+          <t>159039</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>123531</t>
+          <t>135038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>171727</t>
+          <t>186184</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12673,32 +12673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>355114</t>
+          <t>363375</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>314995</t>
+          <t>320296</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>396745</t>
+          <t>404157</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12751,17 +12751,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12786,17 +12786,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12833,32 +12833,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>61938</t>
+          <t>80516</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45378</t>
+          <t>62223</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80381</t>
+          <t>103233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12868,32 +12868,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>86785</t>
+          <t>112708</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51520</t>
+          <t>93298</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108896</t>
+          <t>132410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>148723</t>
+          <t>193225</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114407</t>
+          <t>165828</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>178238</t>
+          <t>224841</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -12946,32 +12946,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88563</t>
+          <t>99828</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67930</t>
+          <t>78266</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>110439</t>
+          <t>123430</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12981,32 +12981,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>151320</t>
+          <t>168429</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93087</t>
+          <t>146038</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181457</t>
+          <t>189777</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13016,32 +13016,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>239883</t>
+          <t>268257</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>181968</t>
+          <t>236112</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>274951</t>
+          <t>299235</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -13059,32 +13059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>273046</t>
+          <t>296546</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>248251</t>
+          <t>268677</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>298668</t>
+          <t>323761</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13094,32 +13094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>272491</t>
+          <t>218966</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>228270</t>
+          <t>199219</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>372249</t>
+          <t>245738</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13129,32 +13129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>545537</t>
+          <t>515512</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>499950</t>
+          <t>478103</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>633839</t>
+          <t>549143</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>56,21%</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13207,17 +13207,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>510596</t>
+          <t>500103</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>510596</t>
+          <t>500103</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>510596</t>
+          <t>500103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -13242,17 +13242,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>934143</t>
+          <t>976994</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>934143</t>
+          <t>976994</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>934143</t>
+          <t>976994</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13289,32 +13289,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>80255</t>
+          <t>110471</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65557</t>
+          <t>93467</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97290</t>
+          <t>134119</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13324,32 +13324,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>129430</t>
+          <t>161419</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113018</t>
+          <t>143052</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>146583</t>
+          <t>181370</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13359,32 +13359,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>209685</t>
+          <t>271891</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>189167</t>
+          <t>245277</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>234729</t>
+          <t>299806</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -13402,32 +13402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>114856</t>
+          <t>129221</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96436</t>
+          <t>108657</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134316</t>
+          <t>151098</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13437,32 +13437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>190690</t>
+          <t>210207</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>173139</t>
+          <t>191623</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>209237</t>
+          <t>230154</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13472,32 +13472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>305546</t>
+          <t>339429</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>278344</t>
+          <t>311710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>331447</t>
+          <t>370691</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -13515,32 +13515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>341063</t>
+          <t>379966</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>318446</t>
+          <t>354114</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>364152</t>
+          <t>405798</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13550,32 +13550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>220895</t>
+          <t>248887</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201890</t>
+          <t>229217</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>239770</t>
+          <t>269628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13585,32 +13585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>561958</t>
+          <t>628854</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>532055</t>
+          <t>594448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>593359</t>
+          <t>663212</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>53,48%</t>
         </is>
       </c>
     </row>
@@ -13628,17 +13628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13663,17 +13663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>541015</t>
+          <t>620514</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>541015</t>
+          <t>620514</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>541015</t>
+          <t>620514</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1077188</t>
+          <t>1240173</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1077188</t>
+          <t>1240173</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1077188</t>
+          <t>1240173</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13745,32 +13745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>91066</t>
+          <t>116593</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42394</t>
+          <t>97599</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133647</t>
+          <t>136400</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>214478</t>
+          <t>199893</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>184313</t>
+          <t>179831</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>301506</t>
+          <t>220243</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13815,32 +13815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>305544</t>
+          <t>316485</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>189522</t>
+          <t>287390</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>389012</t>
+          <t>343187</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -13858,32 +13858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>150682</t>
+          <t>167097</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74912</t>
+          <t>143111</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>217422</t>
+          <t>189237</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>222826</t>
+          <t>236008</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186985</t>
+          <t>216266</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>246379</t>
+          <t>256084</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13928,32 +13928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>373509</t>
+          <t>403104</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>233020</t>
+          <t>372867</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>456634</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -13971,32 +13971,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>641750</t>
+          <t>412561</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>538883</t>
+          <t>384759</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>764126</t>
+          <t>436649</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14006,32 +14006,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>274913</t>
+          <t>300284</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>228880</t>
+          <t>279104</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>300180</t>
+          <t>322570</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14041,32 +14041,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>916664</t>
+          <t>712844</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>775716</t>
+          <t>679793</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1182698</t>
+          <t>749866</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>52,35%</t>
         </is>
       </c>
     </row>
@@ -14084,17 +14084,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>883499</t>
+          <t>696250</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>883499</t>
+          <t>696250</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>883499</t>
+          <t>696250</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>712218</t>
+          <t>736184</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712218</t>
+          <t>736184</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>712218</t>
+          <t>736184</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -14154,17 +14154,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1595717</t>
+          <t>1432434</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1595717</t>
+          <t>1432434</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1595717</t>
+          <t>1432434</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14201,32 +14201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>84350</t>
+          <t>100534</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70571</t>
+          <t>83710</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101692</t>
+          <t>117605</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14236,32 +14236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>169134</t>
+          <t>187510</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153885</t>
+          <t>171377</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>185424</t>
+          <t>206075</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14271,32 +14271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>253484</t>
+          <t>288044</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>231921</t>
+          <t>262881</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>276518</t>
+          <t>314652</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -14314,32 +14314,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>152951</t>
+          <t>162172</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>133779</t>
+          <t>141753</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>171122</t>
+          <t>182821</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14349,32 +14349,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>186066</t>
+          <t>207875</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>169826</t>
+          <t>190467</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>201931</t>
+          <t>226493</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14384,32 +14384,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>339017</t>
+          <t>370047</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>312554</t>
+          <t>342234</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>363452</t>
+          <t>397671</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -14427,32 +14427,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>322903</t>
+          <t>345559</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>301425</t>
+          <t>325365</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>344197</t>
+          <t>368638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14462,32 +14462,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>189105</t>
+          <t>211382</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>172965</t>
+          <t>194224</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204594</t>
+          <t>228256</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14497,32 +14497,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>512008</t>
+          <t>556941</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>484810</t>
+          <t>522563</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>539160</t>
+          <t>585409</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -14540,17 +14540,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14575,17 +14575,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>544305</t>
+          <t>606767</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>544305</t>
+          <t>606767</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>544305</t>
+          <t>606767</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14610,17 +14610,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1104509</t>
+          <t>1215032</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1104509</t>
+          <t>1215032</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1104509</t>
+          <t>1215032</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14657,32 +14657,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>59674</t>
+          <t>66173</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>55465</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>71352</t>
+          <t>80507</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14692,32 +14692,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>163495</t>
+          <t>175925</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>65445</t>
+          <t>161066</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>252587</t>
+          <t>191473</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14727,32 +14727,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>223168</t>
+          <t>242097</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>109965</t>
+          <t>223266</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>291409</t>
+          <t>261976</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -14770,32 +14770,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>93566</t>
+          <t>103801</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>80611</t>
+          <t>88989</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107309</t>
+          <t>118440</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14805,32 +14805,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>133940</t>
+          <t>148025</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52687</t>
+          <t>134018</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>208662</t>
+          <t>163230</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14840,32 +14840,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>227505</t>
+          <t>251826</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>114887</t>
+          <t>231682</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>294124</t>
+          <t>271450</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -14883,32 +14883,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>214050</t>
+          <t>236180</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>198495</t>
+          <t>218884</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>228994</t>
+          <t>254432</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14918,32 +14918,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>310337</t>
+          <t>114537</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>153774</t>
+          <t>101974</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>492074</t>
+          <t>127865</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14953,32 +14953,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>524387</t>
+          <t>350717</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>396074</t>
+          <t>329674</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>750887</t>
+          <t>373437</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -14996,17 +14996,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>367289</t>
+          <t>406154</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>367289</t>
+          <t>406154</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>367289</t>
+          <t>406154</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>607772</t>
+          <t>438487</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>607772</t>
+          <t>438487</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>607772</t>
+          <t>438487</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15066,17 +15066,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>975061</t>
+          <t>844641</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>975061</t>
+          <t>844641</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>975061</t>
+          <t>844641</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15113,32 +15113,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>52854</t>
+          <t>57325</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>42756</t>
+          <t>47048</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>63700</t>
+          <t>69852</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15148,32 +15148,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>213180</t>
+          <t>230199</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>198715</t>
+          <t>215151</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>227711</t>
+          <t>247067</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15183,32 +15183,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>266035</t>
+          <t>287524</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>249263</t>
+          <t>268656</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>286583</t>
+          <t>308531</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -15226,32 +15226,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>107753</t>
+          <t>118158</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>94436</t>
+          <t>102729</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>121063</t>
+          <t>132272</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15261,32 +15261,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>163757</t>
+          <t>178981</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>148723</t>
+          <t>162701</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>178448</t>
+          <t>194854</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15296,32 +15296,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>271510</t>
+          <t>297139</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>252921</t>
+          <t>277122</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>291418</t>
+          <t>319011</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -15339,32 +15339,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>122152</t>
+          <t>134715</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>108863</t>
+          <t>120253</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>134634</t>
+          <t>150655</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15374,32 +15374,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>46926</t>
+          <t>53131</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>38291</t>
+          <t>43182</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>56427</t>
+          <t>64272</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15409,32 +15409,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>169078</t>
+          <t>187847</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>149821</t>
+          <t>169975</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>185239</t>
+          <t>205615</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>423863</t>
+          <t>462311</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>423863</t>
+          <t>462311</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>423863</t>
+          <t>462311</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15522,17 +15522,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>706622</t>
+          <t>772510</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>706622</t>
+          <t>772510</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>706622</t>
+          <t>772510</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15569,32 +15569,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>501907</t>
+          <t>620735</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>383287</t>
+          <t>573167</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>558848</t>
+          <t>673246</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15604,32 +15604,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1069426</t>
+          <t>1186464</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>890681</t>
+          <t>1135671</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1170070</t>
+          <t>1236540</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15639,32 +15639,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1571333</t>
+          <t>1807199</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1351442</t>
+          <t>1730388</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1693041</t>
+          <t>1888447</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -15682,32 +15682,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>827929</t>
+          <t>894611</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>619525</t>
+          <t>839228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>910305</t>
+          <t>950519</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15717,32 +15717,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1122419</t>
+          <t>1234188</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>901031</t>
+          <t>1188050</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1212287</t>
+          <t>1285005</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15752,32 +15752,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1950349</t>
+          <t>2128799</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1646294</t>
+          <t>2053410</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2089340</t>
+          <t>2203237</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -15795,32 +15795,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2123623</t>
+          <t>2009863</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2003440</t>
+          <t>1945994</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2454165</t>
+          <t>2077599</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15830,32 +15830,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1461122</t>
+          <t>1306227</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1293512</t>
+          <t>1254090</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1861306</t>
+          <t>1359916</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15865,32 +15865,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>3584745</t>
+          <t>3316090</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3354584</t>
+          <t>3233662</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4110669</t>
+          <t>3410022</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -15908,17 +15908,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3453459</t>
+          <t>3525209</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3453459</t>
+          <t>3525209</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3453459</t>
+          <t>3525209</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15943,17 +15943,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3652968</t>
+          <t>3726879</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3652968</t>
+          <t>3726879</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3652968</t>
+          <t>3726879</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15978,17 +15978,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7106427</t>
+          <t>7252088</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7106427</t>
+          <t>7252088</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7106427</t>
+          <t>7252088</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
